--- a/shinproduct/신상품 리스트_20260727.xlsx
+++ b/shinproduct/신상품 리스트_20260727.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\AI TEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D182A2-03E0-4B04-86F5-AA9B976219AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757DDA77-BF4F-480C-BB07-0518FE27FF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{31470F2F-4732-4BE9-A3A5-BB882F71415F}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{31470F2F-4732-4BE9-A3A5-BB882F71415F}"/>
   </bookViews>
   <sheets>
     <sheet name="신상품list" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="155">
   <si>
     <t>물품 코드</t>
   </si>
@@ -616,6 +616,10 @@
   </si>
   <si>
     <t>비락</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가루쌀 일반빵</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1164,7 +1168,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.09765625" style="2" customWidth="1"/>
-    <col min="2" max="4" width="17.19921875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.19921875" style="2" customWidth="1"/>
+    <col min="3" max="4" width="17.19921875" style="2" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="13.09765625" style="2" customWidth="1"/>
     <col min="6" max="6" width="62.3984375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5" style="2" customWidth="1"/>
@@ -2208,7 +2213,7 @@
         <v>30</v>
       </c>
       <c r="H40" s="9">
-        <v>46296</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.4">
@@ -2231,7 +2236,7 @@
         <v>151</v>
       </c>
       <c r="H41" s="9">
-        <v>46321</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.4">
@@ -2323,7 +2328,30 @@
         <v>153</v>
       </c>
       <c r="H45" s="9">
-        <v>46314</v>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B46" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="H46" s="9">
+        <v>46321</v>
       </c>
     </row>
     <row r="1048576" spans="2:7" x14ac:dyDescent="0.4">
